--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -620,7 +620,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -905,6 +905,13 @@
   </si>
   <si>
     <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１．バイタルサイン・基本情報、中分類１．バイタルサインの「焦点」</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationVitalSignsCategory_CS"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationVitalSignsCategory_VS</t>
@@ -4562,7 +4569,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -5327,7 +5334,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -5346,7 +5353,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5399,7 +5406,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>205</v>
@@ -5517,7 +5524,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>212</v>
@@ -5637,7 +5644,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>218</v>
@@ -5759,7 +5766,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>228</v>
@@ -5877,7 +5884,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>230</v>
@@ -5997,7 +6004,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>232</v>
@@ -6008,7 +6015,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -6042,10 +6049,10 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>83</v>
@@ -6119,7 +6126,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>242</v>
@@ -6239,7 +6246,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>250</v>
@@ -6359,7 +6366,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>259</v>
@@ -6479,7 +6486,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>267</v>
@@ -6601,7 +6608,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>277</v>
@@ -6723,14 +6730,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6752,16 +6759,16 @@
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6790,7 +6797,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6808,7 +6815,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -6823,30 +6830,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6869,19 +6876,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6930,7 +6937,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6945,19 +6952,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -6965,10 +6972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6991,16 +6998,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7050,7 +7057,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7071,13 +7078,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7085,14 +7092,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7111,19 +7118,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7172,7 +7179,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7187,19 +7194,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7207,14 +7214,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7233,19 +7240,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7294,7 +7301,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7309,19 +7316,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7329,10 +7336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7355,16 +7362,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7414,7 +7421,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7435,13 +7442,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7449,10 +7456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7475,19 +7482,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7536,7 +7543,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7551,19 +7558,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7571,10 +7578,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7597,19 +7604,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7658,7 +7665,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7667,7 +7674,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7676,27 +7683,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7722,16 +7729,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7756,13 +7763,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7780,7 +7787,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7789,7 +7796,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7804,7 +7811,7 @@
         <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7815,14 +7822,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7844,16 +7851,16 @@
         <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7878,13 +7885,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7902,7 +7909,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7920,27 +7927,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7963,19 +7970,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8024,7 +8031,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8045,10 +8052,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8059,10 +8066,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8088,13 +8095,13 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8120,13 +8127,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8144,7 +8151,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8162,27 +8169,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8208,16 +8215,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8242,13 +8249,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8266,7 +8273,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8287,10 +8294,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8301,10 +8308,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8327,16 +8334,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8386,7 +8393,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8404,27 +8411,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8447,16 +8454,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8506,7 +8513,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8524,27 +8531,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8567,19 +8574,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8628,7 +8635,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8640,7 +8647,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8649,10 +8656,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8663,10 +8670,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8781,10 +8788,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8901,14 +8908,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8930,10 +8937,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -8988,7 +8995,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9023,10 +9030,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9049,13 +9056,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9106,7 +9113,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9115,7 +9122,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9127,10 +9134,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9141,10 +9148,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9167,13 +9174,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9224,7 +9231,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9233,7 +9240,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9245,10 +9252,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9259,10 +9266,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9288,16 +9295,16 @@
         <v>188</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9325,10 +9332,10 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9346,7 +9353,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9364,13 +9371,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9381,10 +9388,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9410,16 +9417,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9444,13 +9451,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9468,7 +9475,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9486,13 +9493,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9503,10 +9510,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9529,17 +9536,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9588,7 +9595,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9612,7 +9619,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9623,10 +9630,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9652,10 +9659,10 @@
         <v>206</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9706,7 +9713,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9727,10 +9734,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9741,10 +9748,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9767,16 +9774,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9826,7 +9833,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9847,10 +9854,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9861,10 +9868,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9887,16 +9894,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9946,7 +9953,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9967,10 +9974,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9981,10 +9988,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10007,19 +10014,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10068,7 +10075,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10089,10 +10096,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10103,10 +10110,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10221,10 +10228,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10341,14 +10348,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10370,10 +10377,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10428,7 +10435,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10463,10 +10470,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10492,16 +10499,16 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10530,7 +10537,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10548,7 +10555,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10566,16 +10573,16 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -10583,10 +10590,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10609,19 +10616,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10670,7 +10677,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10688,27 +10695,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10734,16 +10741,16 @@
         <v>188</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10768,13 +10775,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10792,7 +10799,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10801,7 +10808,7 @@
         <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>106</v>
@@ -10816,7 +10823,7 @@
         <v>137</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10827,14 +10834,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10856,16 +10863,16 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10890,13 +10897,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10914,7 +10921,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10932,27 +10939,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10978,16 +10985,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11036,7 +11043,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11057,10 +11064,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -648,6 +648,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="vital-signs"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -802,9 +810,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>vital-signs</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1357,7 +1362,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -3888,7 +3893,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3907,7 +3912,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3960,10 +3965,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3986,13 +3991,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4043,7 +4048,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4067,7 +4072,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4078,10 +4083,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4110,7 +4115,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4151,10 +4156,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4163,7 +4168,7 @@
         <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4187,7 +4192,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4198,10 +4203,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4224,19 +4229,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4285,7 +4290,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4306,10 +4311,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4320,10 +4325,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4346,13 +4351,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4403,7 +4408,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4427,7 +4432,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4438,10 +4443,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4470,7 +4475,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4511,10 +4516,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4523,7 +4528,7 @@
         <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4547,7 +4552,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4558,10 +4563,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4587,23 +4592,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4645,7 +4650,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4666,10 +4671,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4680,10 +4685,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4706,16 +4711,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4765,7 +4770,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4786,10 +4791,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4800,10 +4805,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4829,21 +4834,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>254</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4946,7 +4951,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>260</v>
@@ -5188,7 +5193,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>278</v>
@@ -5409,7 +5414,7 @@
         <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5432,13 +5437,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5489,7 +5494,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5513,7 +5518,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5527,7 +5532,7 @@
         <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5556,7 +5561,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5597,10 +5602,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5609,7 +5614,7 @@
         <v>195</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5633,7 +5638,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5647,7 +5652,7 @@
         <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5670,19 +5675,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5731,7 +5736,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5752,10 +5757,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5769,7 +5774,7 @@
         <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5792,13 +5797,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5849,7 +5854,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5873,7 +5878,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5887,7 +5892,7 @@
         <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5916,7 +5921,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -5957,10 +5962,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -5969,7 +5974,7 @@
         <v>195</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5993,7 +5998,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6007,7 +6012,7 @@
         <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6033,16 +6038,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6091,7 +6096,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6112,10 +6117,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6129,7 +6134,7 @@
         <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6152,16 +6157,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6211,7 +6216,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6232,10 +6237,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6249,7 +6254,7 @@
         <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6275,14 +6280,14 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6392,7 +6397,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>260</v>
@@ -6634,7 +6639,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>278</v>
@@ -8696,13 +8701,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8753,7 +8758,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8777,7 +8782,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8820,7 +8825,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8873,7 +8878,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8897,7 +8902,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9656,7 +9661,7 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>484</v>
@@ -10136,13 +10141,13 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10193,7 +10198,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10217,7 +10222,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10260,7 +10265,7 @@
         <v>141</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>143</v>
@@ -10313,7 +10318,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10337,7 +10342,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-vitalsigns.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-vitalsigns.xlsx
@@ -909,7 +909,7 @@
     <t>second</t>
   </si>
   <si>
-    <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１．バイタルサイン・基本情報、中分類１．バイタルサインの「焦点」</t>
+    <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１、バイタルサイン・基本情報、中分類１、バイタルサインの「焦点」</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -968,7 +968,7 @@
     <t>このObservationの対象を特定するコード</t>
   </si>
   <si>
-    <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１．バイタルサイン・基本情報、中分類１．バイタルサインの「観察名称」</t>
+    <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１、バイタルサイン・基本情報、中分類１、バイタルサインの「観察名称」</t>
   </si>
   <si>
     <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
